--- a/data/trans_orig/AIRE_1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023</t>
+          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>771</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>866</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9115</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>4741</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>839</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7567</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>934</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7797</t>
+          <t>8973</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>11297</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>12216</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19308</t>
+          <t>18384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5173</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16863</t>
+          <t>17226</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35852</t>
+          <t>30924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10232</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40712</t>
+          <t>41334</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>109602</t>
+          <t>109726</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136999</t>
+          <t>136360</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>129095</t>
+          <t>130243</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>145234</t>
+          <t>144941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>247837</t>
+          <t>246357</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>278663</t>
+          <t>278515</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8265</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11654</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24788</t>
+          <t>23174</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>806</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8123</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27698</t>
+          <t>27549</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>884</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>841</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>875</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9223</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30946</t>
+          <t>28782</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34781</t>
+          <t>33144</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19959</t>
+          <t>20113</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18762</t>
+          <t>19440</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>57245</t>
+          <t>53938</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10460</t>
+          <t>10515</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26675</t>
+          <t>26121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35067</t>
+          <t>33620</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>74011</t>
+          <t>71633</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21817</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>27170</t>
+          <t>27135</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>175003</t>
+          <t>176345</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>216669</t>
+          <t>216343</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>169442</t>
+          <t>169291</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>193913</t>
+          <t>193292</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>355226</t>
+          <t>355082</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>403368</t>
+          <t>402299</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3789,12 +3789,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3804,12 +3804,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4015,12 +4015,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4241,12 +4241,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4256,12 +4256,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4276,12 +4276,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4291,12 +4291,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1675</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>8067</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>431</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8987</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4693,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>22260</t>
+          <t>23511</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>16930</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>34840</t>
+          <t>35542</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>43343</t>
+          <t>44825</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>22082</t>
+          <t>22442</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>41868</t>
+          <t>41177</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>49310</t>
+          <t>47725</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>78594</t>
+          <t>78720</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>123333</t>
+          <t>122975</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>148812</t>
+          <t>148753</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>123504</t>
+          <t>123378</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>145442</t>
+          <t>144351</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>254872</t>
+          <t>254651</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>287861</t>
+          <t>287858</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>12522</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>2420</t>
+          <t>2836</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>769</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -5375,12 +5375,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5390,12 +5390,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>12123</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>17330</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,67 +5842,67 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>2709</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>7053</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="J49" s="2" t="inlineStr">
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="R49" s="2" t="inlineStr">
         <is>
           <t>2709</t>
         </is>
       </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>805</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr">
-        <is>
-          <t>6643</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>2709</t>
-        </is>
-      </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>835</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>29592</t>
+          <t>28054</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>18218</t>
+          <t>18087</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>132376</t>
+          <t>115855</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>31625</t>
+          <t>30304</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>152707</t>
+          <t>163292</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>40,79%</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6053,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>16548</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>18448</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>27260</t>
+          <t>24923</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>24292</t>
+          <t>24731</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>44608</t>
+          <t>46582</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>16511</t>
+          <t>16978</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7058</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>21041</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -6392,12 +6392,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>102051</t>
+          <t>102253</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>132226</t>
+          <t>133759</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>78469</t>
+          <t>89160</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>173256</t>
+          <t>173722</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>194413</t>
+          <t>186921</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>294341</t>
+          <t>295240</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,75%</t>
         </is>
       </c>
     </row>
@@ -6622,12 +6622,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6848,12 +6848,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -7001,7 +7001,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7192,7 +7192,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7413,12 +7413,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>7119</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -7639,12 +7639,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>6350</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>11985</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -7752,12 +7752,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>43509</t>
+          <t>44577</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>61132</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7767,82 +7767,82 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
+          <t>43,37%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>59,2%</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>55978</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>48943</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>63704</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>43,52%</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>38,05%</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>49,53%</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>108820</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>97959</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>120012</t>
+        </is>
+      </c>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>47,03%</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
           <t>42,33%</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>59,48%</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>55978</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>48156</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>63463</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>37,44%</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>49,34%</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="R66" s="2" t="inlineStr">
-        <is>
-          <t>108820</t>
-        </is>
-      </c>
-      <c r="S66" s="2" t="inlineStr">
-        <is>
-          <t>97699</t>
-        </is>
-      </c>
-      <c r="T66" s="2" t="inlineStr">
-        <is>
-          <t>119468</t>
-        </is>
-      </c>
-      <c r="U66" s="2" t="inlineStr">
-        <is>
-          <t>47,03%</t>
-        </is>
-      </c>
-      <c r="V66" s="2" t="inlineStr">
-        <is>
-          <t>42,22%</t>
-        </is>
-      </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,86%</t>
         </is>
       </c>
     </row>
@@ -7865,12 +7865,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>37094</t>
+          <t>37177</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>54903</t>
+          <t>53109</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7880,82 +7880,82 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
+          <t>51,68%</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>66354</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>59032</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>73558</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>51,59%</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>45,9%</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>57,19%</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>111296</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>100949</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>123606</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>48,1%</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>43,63%</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
           <t>53,42%</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>66354</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>58778</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>74613</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>51,59%</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>45,7%</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>58,01%</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="R67" s="2" t="inlineStr">
-        <is>
-          <t>111296</t>
-        </is>
-      </c>
-      <c r="S67" s="2" t="inlineStr">
-        <is>
-          <t>101025</t>
-        </is>
-      </c>
-      <c r="T67" s="2" t="inlineStr">
-        <is>
-          <t>123329</t>
-        </is>
-      </c>
-      <c r="U67" s="2" t="inlineStr">
-        <is>
-          <t>48,1%</t>
-        </is>
-      </c>
-      <c r="V67" s="2" t="inlineStr">
-        <is>
-          <t>43,66%</t>
-        </is>
-      </c>
-      <c r="W67" s="2" t="inlineStr">
-        <is>
-          <t>53,3%</t>
         </is>
       </c>
     </row>
@@ -8095,12 +8095,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -8321,12 +8321,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8356,12 +8356,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8434,12 +8434,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8547,12 +8547,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8675,12 +8675,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8773,12 +8773,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8788,12 +8788,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2734</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9014,12 +9014,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9069,12 +9069,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>8270</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -9112,12 +9112,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>14298</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>16528</t>
+          <t>16174</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9162,47 +9162,47 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>18179</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>12244</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>27262</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
           <t>4,35%</t>
         </is>
       </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>11,77%</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R78" s="2" t="inlineStr">
-        <is>
-          <t>18179</t>
-        </is>
-      </c>
-      <c r="S78" s="2" t="inlineStr">
-        <is>
-          <t>12385</t>
-        </is>
-      </c>
-      <c r="T78" s="2" t="inlineStr">
-        <is>
-          <t>26450</t>
-        </is>
-      </c>
-      <c r="U78" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="V78" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -9225,12 +9225,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>29939</t>
+          <t>29989</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9260,12 +9260,12 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>9565</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>22344</t>
+          <t>21986</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>25158</t>
+          <t>25177</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>45638</t>
+          <t>46430</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -9338,12 +9338,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>99680</t>
+          <t>98886</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>118114</t>
+          <t>117618</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -9353,12 +9353,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9373,12 +9373,12 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>102946</t>
+          <t>102997</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>119091</t>
+          <t>119357</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9388,12 +9388,12 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9408,12 +9408,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>208359</t>
+          <t>209010</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>233400</t>
+          <t>233707</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>17155</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>19683</t>
+          <t>20944</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -9681,12 +9681,12 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -9696,12 +9696,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>19730</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>31605</t>
+          <t>31276</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -9794,12 +9794,12 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -9809,12 +9809,12 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -9907,12 +9907,12 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>166</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>6765</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>967</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -10020,12 +10020,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10035,12 +10035,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10075,7 +10075,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10090,12 +10090,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>581</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -10133,12 +10133,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>16603</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10168,12 +10168,12 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>1579</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>17453</t>
+          <t>17332</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10183,12 +10183,12 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10203,12 +10203,12 @@
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>29164</t>
+          <t>29652</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -10246,12 +10246,12 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>10860</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10281,12 +10281,12 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>13073</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -10296,12 +10296,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10316,12 +10316,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>17745</t>
+          <t>17294</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10331,12 +10331,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -10359,12 +10359,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>16448</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10394,12 +10394,12 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>28701</t>
+          <t>26818</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -10409,12 +10409,12 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10429,12 +10429,12 @@
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>9771</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>35256</t>
+          <t>36071</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -10444,12 +10444,12 @@
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -10472,12 +10472,12 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>20820</t>
+          <t>19523</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10507,12 +10507,12 @@
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>13595</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10522,12 +10522,12 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>27920</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10557,12 +10557,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -10585,12 +10585,12 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>27076</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10620,12 +10620,12 @@
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>25673</t>
+          <t>25158</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -10635,12 +10635,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10655,12 +10655,12 @@
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>12223</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>45925</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -10698,12 +10698,12 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>27774</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10733,12 +10733,12 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>53628</t>
+          <t>52395</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10768,12 +10768,12 @@
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>18173</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>68741</t>
+          <t>67750</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -10811,12 +10811,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>179994</t>
+          <t>182831</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>214973</t>
+          <t>217889</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10846,12 +10846,12 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>330040</t>
+          <t>329655</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>463327</t>
+          <t>464391</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -10861,12 +10861,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10881,12 +10881,12 @@
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>527399</t>
+          <t>531050</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>691676</t>
+          <t>692296</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -11041,12 +11041,12 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -11126,12 +11126,12 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11154,12 +11154,12 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="S96" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11239,12 +11239,12 @@
       </c>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11267,12 +11267,12 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11317,12 +11317,12 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="S97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U97" s="2" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11380,12 +11380,12 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -11415,12 +11415,12 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -11430,12 +11430,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -11450,12 +11450,12 @@
       </c>
       <c r="S98" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11493,12 +11493,12 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -11543,12 +11543,12 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -11563,12 +11563,12 @@
       </c>
       <c r="S99" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11606,12 +11606,12 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="S100" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11719,12 +11719,12 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -11769,12 +11769,12 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11789,12 +11789,12 @@
       </c>
       <c r="S101" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11832,12 +11832,12 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -11847,12 +11847,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -11945,12 +11945,12 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -11960,12 +11960,12 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
@@ -12058,12 +12058,12 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>13214</t>
+          <t>12640</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -12073,12 +12073,12 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12093,12 +12093,12 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>729</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12128,12 +12128,12 @@
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -12171,12 +12171,12 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>41406</t>
+          <t>41736</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>66078</t>
+          <t>66965</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -12186,12 +12186,12 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12206,12 +12206,12 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>21237</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>37882</t>
+          <t>38551</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
@@ -12221,12 +12221,12 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>68622</t>
+          <t>67344</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>98601</t>
+          <t>96796</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -12256,12 +12256,12 @@
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -12284,12 +12284,12 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>268789</t>
+          <t>268836</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>295765</t>
+          <t>296048</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -12299,12 +12299,12 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12319,12 +12319,12 @@
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>291700</t>
+          <t>291249</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>308710</t>
+          <t>309707</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -12334,12 +12334,12 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12354,12 +12354,12 @@
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>567291</t>
+          <t>568594</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>598969</t>
+          <t>599940</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -12514,12 +12514,12 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>21226</t>
+          <t>20482</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -12529,12 +12529,12 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
@@ -12549,12 +12549,12 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -12584,12 +12584,12 @@
       </c>
       <c r="S108" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="T108" s="2" t="inlineStr">
         <is>
-          <t>35654</t>
+          <t>34500</t>
         </is>
       </c>
       <c r="U108" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -12627,12 +12627,12 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>14496</t>
+          <t>14063</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>43730</t>
+          <t>39894</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -12642,12 +12642,12 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -12662,12 +12662,12 @@
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>8593</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>23820</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -12677,12 +12677,12 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -12697,12 +12697,12 @@
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>25885</t>
+          <t>26686</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>56925</t>
+          <t>60935</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -12712,12 +12712,12 @@
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -12740,12 +12740,12 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -12755,12 +12755,12 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
@@ -12853,12 +12853,12 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>480</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -12868,12 +12868,12 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -12903,47 +12903,47 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R111" s="2" t="inlineStr">
+        <is>
+          <t>6958</t>
+        </is>
+      </c>
+      <c r="S111" s="2" t="inlineStr">
+        <is>
+          <t>2988</t>
+        </is>
+      </c>
+      <c r="T111" s="2" t="inlineStr">
+        <is>
+          <t>14177</t>
+        </is>
+      </c>
+      <c r="U111" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
           <t>0,08%</t>
         </is>
       </c>
-      <c r="P111" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="Q111" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R111" s="2" t="inlineStr">
-        <is>
-          <t>6958</t>
-        </is>
-      </c>
-      <c r="S111" s="2" t="inlineStr">
-        <is>
-          <t>2989</t>
-        </is>
-      </c>
-      <c r="T111" s="2" t="inlineStr">
-        <is>
-          <t>15528</t>
-        </is>
-      </c>
-      <c r="U111" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V111" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
       <c r="W111" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -12966,12 +12966,12 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -12981,74 +12981,74 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>1256</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>8808</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>9455</t>
+        </is>
+      </c>
+      <c r="U112" s="2" t="inlineStr">
+        <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="M112" s="2" t="inlineStr">
-        <is>
-          <t>9435</t>
-        </is>
-      </c>
-      <c r="N112" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O112" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="P112" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="Q112" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R112" s="2" t="inlineStr">
-        <is>
-          <t>3950</t>
-        </is>
-      </c>
-      <c r="S112" s="2" t="inlineStr">
-        <is>
-          <t>1382</t>
-        </is>
-      </c>
-      <c r="T112" s="2" t="inlineStr">
-        <is>
-          <t>9165</t>
-        </is>
-      </c>
-      <c r="U112" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
       <c r="V112" s="2" t="inlineStr">
         <is>
           <t>0,04%</t>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="W112" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -13079,12 +13079,12 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>30913</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -13094,12 +13094,12 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -13114,12 +13114,12 @@
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>27779</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
@@ -13129,12 +13129,12 @@
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -13149,12 +13149,12 @@
       </c>
       <c r="S113" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>26150</t>
         </is>
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>49676</t>
+          <t>50470</t>
         </is>
       </c>
       <c r="U113" s="2" t="inlineStr">
@@ -13164,12 +13164,12 @@
       </c>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -13192,12 +13192,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>18808</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -13207,12 +13207,12 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -13242,12 +13242,12 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -13262,12 +13262,12 @@
       </c>
       <c r="S114" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="T114" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="U114" s="2" t="inlineStr">
@@ -13305,12 +13305,12 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>28884</t>
+          <t>27483</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>65897</t>
+          <t>66248</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -13320,12 +13320,12 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -13340,12 +13340,12 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>39635</t>
+          <t>39148</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>218708</t>
+          <t>193213</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
@@ -13355,12 +13355,12 @@
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -13375,12 +13375,12 @@
       </c>
       <c r="S115" s="2" t="inlineStr">
         <is>
-          <t>80025</t>
+          <t>79237</t>
         </is>
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>239294</t>
+          <t>258990</t>
         </is>
       </c>
       <c r="U115" s="2" t="inlineStr">
@@ -13390,12 +13390,12 @@
       </c>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -13418,12 +13418,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>25698</t>
+          <t>25010</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>52450</t>
+          <t>52351</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -13433,12 +13433,12 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -13453,12 +13453,12 @@
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>27949</t>
+          <t>28036</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -13468,12 +13468,12 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -13488,12 +13488,12 @@
       </c>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t>40723</t>
+          <t>41144</t>
         </is>
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>73581</t>
+          <t>72978</t>
         </is>
       </c>
       <c r="U116" s="2" t="inlineStr">
@@ -13503,12 +13503,12 @@
       </c>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -13531,12 +13531,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>78520</t>
+          <t>77744</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>134861</t>
+          <t>131878</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -13566,12 +13566,12 @@
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>57592</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>99422</t>
+          <t>99232</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -13581,12 +13581,12 @@
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -13601,12 +13601,12 @@
       </c>
       <c r="S117" s="2" t="inlineStr">
         <is>
-          <t>146865</t>
+          <t>142242</t>
         </is>
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>217481</t>
+          <t>220409</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
@@ -13616,12 +13616,12 @@
       </c>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -13644,12 +13644,12 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>165292</t>
+          <t>166850</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>215195</t>
+          <t>218082</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -13679,12 +13679,12 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>122740</t>
+          <t>122472</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>210604</t>
+          <t>209894</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -13694,12 +13694,12 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -13714,12 +13714,12 @@
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>300038</t>
+          <t>300886</t>
         </is>
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>410084</t>
+          <t>410475</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
@@ -13729,12 +13729,12 @@
       </c>
       <c r="V118" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W118" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -13757,12 +13757,12 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>1173195</t>
+          <t>1172583</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>1257849</t>
+          <t>1257039</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -13792,12 +13792,12 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>1404113</t>
+          <t>1405072</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>1610666</t>
+          <t>1605310</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
@@ -13807,12 +13807,12 @@
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -13827,12 +13827,12 @@
       </c>
       <c r="S119" s="2" t="inlineStr">
         <is>
-          <t>2613514</t>
+          <t>2615583</t>
         </is>
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>2857112</t>
+          <t>2854479</t>
         </is>
       </c>
       <c r="U119" s="2" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="V119" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="W119" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Provincia-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>884</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>472</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1356</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3269</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>8011</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>6089</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9998</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>802</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>480</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3259</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>496</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1516,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11297</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1551,32 +1551,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12216</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>10478</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18384</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1629,32 +1629,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13691</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1664,32 +1664,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7428</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1699,32 +1699,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>11195</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>6615</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>17775</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9254</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1627</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30924</t>
+          <t>17120</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15470</t>
+          <t>13127</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41334</t>
+          <t>23174</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>820</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2319</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8160</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>7416</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -1968,32 +1968,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>126529</t>
+          <t>136743</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>109726</t>
+          <t>125395</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136360</t>
+          <t>144710</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2003,32 +2003,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>138536</t>
+          <t>151180</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>130243</t>
+          <t>143093</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>144941</t>
+          <t>157559</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2038,32 +2038,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>265065</t>
+          <t>287923</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>246357</t>
+          <t>275135</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>278515</t>
+          <t>300432</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -2081,17 +2081,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>157176</t>
+          <t>164558</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157176</t>
+          <t>164558</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>157176</t>
+          <t>164558</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,17 +2116,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>163318</t>
+          <t>177352</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163318</t>
+          <t>177352</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163318</t>
+          <t>177352</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>320494</t>
+          <t>341910</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>320494</t>
+          <t>341910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320494</t>
+          <t>341910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>10581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -2311,69 +2311,69 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23174</t>
+          <t>20306</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3292</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8171</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
           <t>3,31%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3407</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27549</t>
+          <t>26605</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>891</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8463</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3760</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>14345</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -2876,32 +2876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9869</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11799</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2989,22 +2989,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28782</t>
+          <t>25907</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5013</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1668</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>11945</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>16048</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>32146</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20113</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>11284</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -3215,32 +3215,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>33196</t>
+          <t>32245</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53938</t>
+          <t>52640</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3250,32 +3250,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10515</t>
+          <t>10700</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26121</t>
+          <t>26852</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>49806</t>
+          <t>49627</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33620</t>
+          <t>35641</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71633</t>
+          <t>71162</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -3328,32 +3328,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10894</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3363,32 +3363,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>12316</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20647</t>
+          <t>25315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3398,32 +3398,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>16211</t>
+          <t>17712</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>27135</t>
+          <t>29083</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -3441,32 +3441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>197856</t>
+          <t>198346</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>176345</t>
+          <t>174877</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>216343</t>
+          <t>217040</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3476,32 +3476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>183008</t>
+          <t>193887</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>169291</t>
+          <t>179855</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>193292</t>
+          <t>204714</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3511,32 +3511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>380864</t>
+          <t>392233</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>355082</t>
+          <t>368719</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>402299</t>
+          <t>414404</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,72%</t>
         </is>
       </c>
     </row>
@@ -3554,17 +3554,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>272340</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>272340</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>272340</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,17 +3589,17 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>233994</t>
+          <t>246871</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>233994</t>
+          <t>246871</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>233994</t>
+          <t>246871</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,17 +3624,17 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>506334</t>
+          <t>519813</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>506334</t>
+          <t>519813</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>506334</t>
+          <t>519813</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4409,7 +4409,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -4472,12 +4472,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4497,22 +4497,22 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>450</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4155</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1466</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>11520</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4610,22 +4610,22 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>2610</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>705</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>7831</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,22 +4645,22 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -4688,32 +4688,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>23511</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4723,32 +4723,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>10852</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4758,32 +4758,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>23131</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>14651</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>35542</t>
+          <t>34748</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -4801,32 +4801,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>31778</t>
+          <t>30137</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>21765</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>44825</t>
+          <t>42068</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>30886</t>
+          <t>30320</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>22442</t>
+          <t>21562</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>41177</t>
+          <t>41068</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>62665</t>
+          <t>60458</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>47725</t>
+          <t>46372</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>78720</t>
+          <t>75013</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -4914,32 +4914,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>137186</t>
+          <t>141529</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>122975</t>
+          <t>128286</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>148753</t>
+          <t>152813</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4949,32 +4949,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>134963</t>
+          <t>140595</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>123378</t>
+          <t>128713</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>144351</t>
+          <t>150308</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4984,32 +4984,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>272150</t>
+          <t>282125</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>254651</t>
+          <t>263989</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>287858</t>
+          <t>298403</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>79,14%</t>
         </is>
       </c>
     </row>
@@ -5027,17 +5027,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>186803</t>
+          <t>189949</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>186803</t>
+          <t>189949</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>186803</t>
+          <t>189949</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5062,17 +5062,17 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>181412</t>
+          <t>187099</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>181412</t>
+          <t>187099</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>181412</t>
+          <t>187099</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5097,17 +5097,17 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>368216</t>
+          <t>377049</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>368216</t>
+          <t>377049</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>368216</t>
+          <t>377049</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>2625</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,32 +5214,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>12522</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5257,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5267,59 +5267,59 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8685</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2778</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
           <t>1,26%</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>786</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>2836</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -5327,17 +5327,17 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>815</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9241</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5709,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5364</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5744,32 +5744,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>8263</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>17647</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -5857,32 +5857,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,17 +5892,17 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>909</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5935,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>14314</t>
+          <t>16121</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>32959</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5970,32 +5970,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>51214</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>12935</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>115855</t>
+          <t>33245</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>65527</t>
+          <t>36306</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>30304</t>
+          <t>24014</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>163292</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -6048,32 +6048,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>16548</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6083,32 +6083,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6118,32 +6118,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>18448</t>
+          <t>21073</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -6161,32 +6161,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>17031</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>31771</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6196,32 +6196,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>12677</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>24731</t>
+          <t>26331</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6231,32 +6231,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>30392</t>
+          <t>35394</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>25669</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>46582</t>
+          <t>54282</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -6274,32 +6274,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>9058</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>16978</t>
+          <t>16768</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6309,67 +6309,67 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3626</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>12898</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>7210</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>20843</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
           <t>3,08%</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>12551</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>7055</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>20829</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -6387,32 +6387,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>118697</t>
+          <t>138911</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>102253</t>
+          <t>120228</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>133759</t>
+          <t>153569</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6422,32 +6422,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>144923</t>
+          <t>164976</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>89160</t>
+          <t>151183</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>173722</t>
+          <t>176419</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6457,32 +6457,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>263620</t>
+          <t>303887</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>186921</t>
+          <t>279803</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>295240</t>
+          <t>323052</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>73,75%</t>
+          <t>77,08%</t>
         </is>
       </c>
     </row>
@@ -6500,17 +6500,17 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>171180</t>
+          <t>198685</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>171180</t>
+          <t>198685</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>171180</t>
+          <t>198685</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6535,17 +6535,17 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>229157</t>
+          <t>220453</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>229157</t>
+          <t>220453</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>229157</t>
+          <t>220453</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6570,17 +6570,17 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>400337</t>
+          <t>419138</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>400337</t>
+          <t>419138</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>400337</t>
+          <t>419138</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>455</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -7001,12 +7001,12 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>455</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
@@ -7036,12 +7036,12 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>780</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -7192,12 +7192,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -7207,7 +7207,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>401</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -7227,12 +7227,12 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4293</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>441</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -7453,12 +7453,12 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>441</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -7634,22 +7634,22 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7669,32 +7669,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>9819</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7704,32 +7704,32 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>8693</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>12264</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -7747,32 +7747,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>52841</t>
+          <t>57536</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>44577</t>
+          <t>48019</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>60841</t>
+          <t>66547</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>55978</t>
+          <t>59848</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>48943</t>
+          <t>51300</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>63704</t>
+          <t>68071</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>108820</t>
+          <t>117385</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>97959</t>
+          <t>105616</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>120012</t>
+          <t>129266</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,33%</t>
         </is>
       </c>
     </row>
@@ -7860,32 +7860,32 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>37177</t>
+          <t>41580</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>53109</t>
+          <t>59975</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>66354</t>
+          <t>71458</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>59032</t>
+          <t>63488</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>73558</t>
+          <t>79598</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7930,32 +7930,32 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>111296</t>
+          <t>121763</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>100949</t>
+          <t>109975</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>123606</t>
+          <t>134367</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -7973,17 +7973,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>102774</t>
+          <t>113244</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>102774</t>
+          <t>113244</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>102774</t>
+          <t>113244</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>128622</t>
+          <t>138580</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>128622</t>
+          <t>138580</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>128622</t>
+          <t>138580</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8043,17 +8043,17 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>231396</t>
+          <t>251825</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>231396</t>
+          <t>251825</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>231396</t>
+          <t>251825</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>548</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>2741</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>625</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
@@ -8283,12 +8283,12 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>498</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -8926,12 +8926,12 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -8994,22 +8994,22 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>2475</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9064,32 +9064,32 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -9107,32 +9107,32 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>13286</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -9142,32 +9142,32 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>10148</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>16093</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9177,32 +9177,32 @@
       </c>
       <c r="R78" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>18028</t>
         </is>
       </c>
       <c r="S78" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>12012</t>
         </is>
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>27262</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -9220,32 +9220,32 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>28452</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9255,32 +9255,32 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>21986</t>
+          <t>23116</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9290,32 +9290,32 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>34764</t>
+          <t>34197</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>25177</t>
+          <t>25447</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>46430</t>
+          <t>45769</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -9333,32 +9333,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>109355</t>
+          <t>109283</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>98886</t>
+          <t>98812</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>117618</t>
+          <t>116890</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9368,32 +9368,32 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>112622</t>
+          <t>115202</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>102997</t>
+          <t>105881</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>119357</t>
+          <t>122647</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9403,32 +9403,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>221978</t>
+          <t>224485</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>209010</t>
+          <t>211857</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>233707</t>
+          <t>235653</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -9446,17 +9446,17 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>141212</t>
+          <t>139964</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>141212</t>
+          <t>139964</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>141212</t>
+          <t>139964</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9481,17 +9481,17 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>140382</t>
+          <t>143274</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>140382</t>
+          <t>143274</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>140382</t>
+          <t>143274</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9516,17 +9516,17 @@
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
-          <t>281594</t>
+          <t>283238</t>
         </is>
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>281594</t>
+          <t>283238</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>281594</t>
+          <t>283238</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9563,32 +9563,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>6614</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>14219</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -9598,32 +9598,32 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>15436</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -9633,32 +9633,32 @@
       </c>
       <c r="R82" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>12702</t>
         </is>
       </c>
       <c r="S82" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="T82" s="2" t="inlineStr">
         <is>
-          <t>20944</t>
+          <t>23056</t>
         </is>
       </c>
       <c r="U82" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -9676,32 +9676,32 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>17132</t>
+          <t>22285</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -9711,32 +9711,32 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>11979</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9746,32 +9746,32 @@
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
-          <t>18691</t>
+          <t>24029</t>
         </is>
       </c>
       <c r="S83" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>15624</t>
         </is>
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>31276</t>
+          <t>37321</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="S84" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -9902,32 +9902,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>8009</t>
+          <t>10834</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -9937,32 +9937,32 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2326</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -9972,32 +9972,32 @@
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="S85" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -10050,32 +10050,32 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10085,32 +10085,32 @@
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -10128,32 +10128,32 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>8971</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>16603</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -10163,32 +10163,32 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>7977</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>17332</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10198,32 +10198,32 @@
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
-          <t>16948</t>
+          <t>19033</t>
         </is>
       </c>
       <c r="S87" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>12222</t>
         </is>
       </c>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>29652</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="U87" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -10241,32 +10241,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -10276,32 +10276,32 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>2806</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -10311,32 +10311,32 @@
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
-          <t>9534</t>
+          <t>9878</t>
         </is>
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>17305</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -10354,32 +10354,32 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>16345</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
@@ -10389,32 +10389,32 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>13580</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>26818</t>
+          <t>30079</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -10424,32 +10424,32 @@
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
-          <t>22609</t>
+          <t>28109</t>
         </is>
       </c>
       <c r="S89" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>19501</t>
         </is>
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>36071</t>
+          <t>40680</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -10467,32 +10467,32 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>10937</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>19523</t>
+          <t>21618</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -10502,32 +10502,32 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>13104</t>
+          <t>11626</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10537,32 +10537,32 @@
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>15260</t>
+          <t>16194</t>
         </is>
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>26786</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -10580,32 +10580,32 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>15166</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>12860</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>27076</t>
+          <t>36897</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -10615,32 +10615,32 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>20097</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>25158</t>
+          <t>29297</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -10650,32 +10650,32 @@
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>28299</t>
+          <t>41409</t>
         </is>
       </c>
       <c r="S91" s="2" t="inlineStr">
         <is>
-          <t>12223</t>
+          <t>30311</t>
         </is>
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>45925</t>
+          <t>59401</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -10693,32 +10693,32 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>17307</t>
+          <t>21698</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>13481</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>27755</t>
+          <t>33353</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -10728,32 +10728,32 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>27682</t>
+          <t>34292</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>24481</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>52395</t>
+          <t>46387</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -10763,32 +10763,32 @@
       </c>
       <c r="R92" s="2" t="inlineStr">
         <is>
-          <t>44989</t>
+          <t>55990</t>
         </is>
       </c>
       <c r="S92" s="2" t="inlineStr">
         <is>
-          <t>17994</t>
+          <t>43762</t>
         </is>
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>67750</t>
+          <t>72617</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -10806,32 +10806,32 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>199410</t>
+          <t>220879</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>182831</t>
+          <t>201535</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>217889</t>
+          <t>238969</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -10841,32 +10841,32 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>403939</t>
+          <t>240713</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>329655</t>
+          <t>223575</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>464391</t>
+          <t>256157</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -10876,32 +10876,32 @@
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>603350</t>
+          <t>461593</t>
         </is>
       </c>
       <c r="S93" s="2" t="inlineStr">
         <is>
-          <t>531050</t>
+          <t>434612</t>
         </is>
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>692296</t>
+          <t>484466</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>71,4%</t>
         </is>
       </c>
     </row>
@@ -10919,17 +10919,17 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>280830</t>
+          <t>321543</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>280830</t>
+          <t>321543</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>280830</t>
+          <t>321543</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -10954,17 +10954,17 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>497060</t>
+          <t>357024</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>497060</t>
+          <t>357024</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>497060</t>
+          <t>357024</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10989,17 +10989,17 @@
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>777890</t>
+          <t>678568</t>
         </is>
       </c>
       <c r="S94" s="2" t="inlineStr">
         <is>
-          <t>777890</t>
+          <t>678568</t>
         </is>
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>777890</t>
+          <t>678568</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>973</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -11872,12 +11872,12 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="R102" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>973</t>
         </is>
       </c>
       <c r="S102" s="2" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="V102" s="2" t="inlineStr">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>608</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12010,7 +12010,7 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>608</t>
         </is>
       </c>
       <c r="S103" s="2" t="inlineStr">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -12053,32 +12053,32 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
@@ -12088,32 +12088,32 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>771</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -12123,32 +12123,32 @@
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="S104" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="T104" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -12166,32 +12166,32 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>52578</t>
+          <t>58123</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>41736</t>
+          <t>45832</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>66965</t>
+          <t>73443</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -12201,32 +12201,32 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>29420</t>
+          <t>33600</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>24687</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>38551</t>
+          <t>43401</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -12236,32 +12236,32 @@
       </c>
       <c r="R105" s="2" t="inlineStr">
         <is>
-          <t>81998</t>
+          <t>91723</t>
         </is>
       </c>
       <c r="S105" s="2" t="inlineStr">
         <is>
-          <t>67344</t>
+          <t>74349</t>
         </is>
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>96796</t>
+          <t>109948</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -12279,32 +12279,32 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>283970</t>
+          <t>335232</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>268836</t>
+          <t>319979</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>296048</t>
+          <t>348095</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
@@ -12314,32 +12314,32 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>300655</t>
+          <t>348152</t>
         </is>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>291249</t>
+          <t>337567</t>
         </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>309707</t>
+          <t>357861</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -12349,32 +12349,32 @@
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
-          <t>584626</t>
+          <t>683384</t>
         </is>
       </c>
       <c r="S106" s="2" t="inlineStr">
         <is>
-          <t>568594</t>
+          <t>665458</t>
         </is>
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>599940</t>
+          <t>700488</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -12392,17 +12392,17 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>342719</t>
+          <t>400188</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>342719</t>
+          <t>400188</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>342719</t>
+          <t>400188</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -12427,17 +12427,17 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>333849</t>
+          <t>385827</t>
         </is>
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>333849</t>
+          <t>385827</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>333849</t>
+          <t>385827</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -12462,17 +12462,17 @@
       </c>
       <c r="R107" s="2" t="inlineStr">
         <is>
-          <t>676569</t>
+          <t>786015</t>
         </is>
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>676569</t>
+          <t>786015</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>676569</t>
+          <t>786015</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -12509,102 +12509,102 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>11657</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>20482</t>
+          <t>23549</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>12294</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>6787</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>23261</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>25600</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>17012</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>39584</t>
+        </is>
+      </c>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>11310</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr">
-        <is>
-          <t>5623</t>
-        </is>
-      </c>
-      <c r="M108" s="2" t="inlineStr">
-        <is>
-          <t>21812</t>
-        </is>
-      </c>
-      <c r="N108" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="O108" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P108" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="Q108" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R108" s="2" t="inlineStr">
-        <is>
-          <t>22967</t>
-        </is>
-      </c>
-      <c r="S108" s="2" t="inlineStr">
-        <is>
-          <t>14626</t>
-        </is>
-      </c>
-      <c r="T108" s="2" t="inlineStr">
-        <is>
-          <t>34500</t>
-        </is>
-      </c>
-      <c r="U108" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -12622,32 +12622,32 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>23657</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>16258</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>39894</t>
+          <t>42946</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -12657,32 +12657,32 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>8986</t>
+          <t>10930</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>23820</t>
+          <t>27717</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -12692,32 +12692,32 @@
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="S109" s="2" t="inlineStr">
         <is>
-          <t>26686</t>
+          <t>31420</t>
         </is>
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>60935</t>
+          <t>63188</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -12805,7 +12805,7 @@
       </c>
       <c r="R110" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>715</t>
         </is>
       </c>
       <c r="S110" s="2" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="T110" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="U110" s="2" t="inlineStr">
@@ -12848,32 +12848,32 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -12883,32 +12883,32 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -12918,32 +12918,32 @@
       </c>
       <c r="R111" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>16872</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -12996,27 +12996,27 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>8501</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
@@ -13031,17 +13031,17 @@
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="S112" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="T112" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="U112" s="2" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="W112" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -13074,32 +13074,32 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>19827</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>11960</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>30913</t>
+          <t>30820</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
@@ -13109,32 +13109,32 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>20531</t>
         </is>
       </c>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>13852</t>
         </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>27779</t>
+          <t>29429</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -13144,32 +13144,32 @@
       </c>
       <c r="R113" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>40358</t>
         </is>
       </c>
       <c r="S113" s="2" t="inlineStr">
         <is>
-          <t>26150</t>
+          <t>29655</t>
         </is>
       </c>
       <c r="T113" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>53727</t>
         </is>
       </c>
       <c r="U113" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -13187,97 +13187,97 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>12601</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>7718</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>19903</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>22948</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="inlineStr">
+        <is>
+          <t>15606</t>
+        </is>
+      </c>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>34242</t>
+        </is>
+      </c>
+      <c r="U114" s="2" t="inlineStr">
+        <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>12249</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="inlineStr">
-        <is>
-          <t>7078</t>
-        </is>
-      </c>
-      <c r="M114" s="2" t="inlineStr">
-        <is>
-          <t>19382</t>
-        </is>
-      </c>
-      <c r="N114" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P114" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="Q114" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="R114" s="2" t="inlineStr">
-        <is>
-          <t>22709</t>
-        </is>
-      </c>
-      <c r="S114" s="2" t="inlineStr">
-        <is>
-          <t>14534</t>
-        </is>
-      </c>
-      <c r="T114" s="2" t="inlineStr">
-        <is>
-          <t>33329</t>
-        </is>
-      </c>
-      <c r="U114" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="V114" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W114" s="2" t="inlineStr">
@@ -13300,32 +13300,32 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>46656</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>27483</t>
+          <t>32865</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>66248</t>
+          <t>69958</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
@@ -13335,32 +13335,32 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>51646</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>39148</t>
+          <t>39650</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>193213</t>
+          <t>67758</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -13370,32 +13370,32 @@
       </c>
       <c r="R115" s="2" t="inlineStr">
         <is>
-          <t>120940</t>
+          <t>98302</t>
         </is>
       </c>
       <c r="S115" s="2" t="inlineStr">
         <is>
-          <t>79237</t>
+          <t>77732</t>
         </is>
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>258990</t>
+          <t>127040</t>
         </is>
       </c>
       <c r="U115" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -13413,32 +13413,32 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>37958</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>25010</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>52351</t>
+          <t>55974</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -13448,32 +13448,32 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>28036</t>
+          <t>30193</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -13483,32 +13483,32 @@
       </c>
       <c r="R116" s="2" t="inlineStr">
         <is>
-          <t>55713</t>
+          <t>59629</t>
         </is>
       </c>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>45096</t>
         </is>
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>72978</t>
+          <t>77475</t>
         </is>
       </c>
       <c r="U116" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -13526,32 +13526,32 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>100839</t>
+          <t>106492</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>77744</t>
+          <t>82904</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>131878</t>
+          <t>134298</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
@@ -13561,32 +13561,32 @@
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>80479</t>
+          <t>92052</t>
         </is>
       </c>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>57592</t>
+          <t>78101</t>
         </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>99232</t>
+          <t>110705</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -13596,32 +13596,32 @@
       </c>
       <c r="R117" s="2" t="inlineStr">
         <is>
-          <t>181318</t>
+          <t>198544</t>
         </is>
       </c>
       <c r="S117" s="2" t="inlineStr">
         <is>
-          <t>142242</t>
+          <t>171018</t>
         </is>
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>220409</t>
+          <t>229259</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -13639,32 +13639,32 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>190204</t>
+          <t>204442</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>166850</t>
+          <t>177455</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>218082</t>
+          <t>229810</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -13674,32 +13674,32 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>178265</t>
+          <t>193335</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>122472</t>
+          <t>171171</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>209894</t>
+          <t>217738</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -13709,32 +13709,32 @@
       </c>
       <c r="R118" s="2" t="inlineStr">
         <is>
-          <t>368470</t>
+          <t>397778</t>
         </is>
       </c>
       <c r="S118" s="2" t="inlineStr">
         <is>
-          <t>300886</t>
+          <t>364134</t>
         </is>
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>410475</t>
+          <t>436288</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="V118" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W118" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -13752,32 +13752,32 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>1217946</t>
+          <t>1331230</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>1172583</t>
+          <t>1284265</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>1257039</t>
+          <t>1369981</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,91%</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
@@ -13787,32 +13787,32 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>1485002</t>
+          <t>1426164</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>1405072</t>
+          <t>1391742</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>1605310</t>
+          <t>1458383</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -13822,32 +13822,32 @@
       </c>
       <c r="R119" s="2" t="inlineStr">
         <is>
-          <t>2702949</t>
+          <t>2757393</t>
         </is>
       </c>
       <c r="S119" s="2" t="inlineStr">
         <is>
-          <t>2615583</t>
+          <t>2704879</t>
         </is>
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>2854479</t>
+          <t>2809037</t>
         </is>
       </c>
       <c r="U119" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="V119" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="W119" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -13865,17 +13865,17 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>1655035</t>
+          <t>1801075</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -13900,17 +13900,17 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>1907795</t>
+          <t>1856481</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -13935,17 +13935,17 @@
       </c>
       <c r="R120" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="S120" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>3562831</t>
+          <t>3657555</t>
         </is>
       </c>
       <c r="U120" s="2" t="inlineStr">

--- a/data/trans_orig/AIRE_1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que estarían dispuestos a pagar al año para que la administración pública ponga en marcha actuaciones (+++) en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según lo que estaría dispuesta a pagar al año para que la administración pública ponga en marcha actuaciones en su municipio/ciudad (o lugar de residencia) que haga reducir la contaminación del aire en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
